--- a/Selection Dates.xlsx
+++ b/Selection Dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nico\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nico\naroix\NaroIX-Benchmark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF867B3-BAC3-4136-9831-E48A58EA996D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46C7BA4E-EB49-4777-984C-35249B99396C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{24FF59A1-7234-4942-98D7-B7BE7DF6F0AC}"/>
+    <workbookView xWindow="-13860" yWindow="-16308" windowWidth="29016" windowHeight="15696" xr2:uid="{24FF59A1-7234-4942-98D7-B7BE7DF6F0AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Historcial Data" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>2015-02-18</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>05/20/2026</t>
+  </si>
+  <si>
+    <t>08/19/2026</t>
   </si>
 </sst>
 </file>
@@ -697,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA481E37-1CE1-49C4-A8D4-417DADDFB568}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
@@ -1092,6 +1095,14 @@
         <v>93</v>
       </c>
     </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B50" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
